--- a/Team-Data/2013-14/11-17-2013-14.xlsx
+++ b/Team-Data/2013-14/11-17-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>4.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE2" t="n">
         <v>9</v>
@@ -751,10 +818,10 @@
         <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ2" t="n">
         <v>17</v>
@@ -766,13 +833,13 @@
         <v>10</v>
       </c>
       <c r="AM2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN2" t="n">
         <v>13</v>
       </c>
       <c r="AO2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP2" t="n">
         <v>10</v>
@@ -787,7 +854,7 @@
         <v>8</v>
       </c>
       <c r="AT2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU2" t="n">
         <v>2</v>
@@ -799,7 +866,7 @@
         <v>10</v>
       </c>
       <c r="AX2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY2" t="n">
         <v>7</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -921,19 +988,19 @@
         <v>-3.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI3" t="n">
         <v>19</v>
@@ -954,10 +1021,10 @@
         <v>25</v>
       </c>
       <c r="AO3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ3" t="n">
         <v>12</v>
@@ -966,10 +1033,10 @@
         <v>23</v>
       </c>
       <c r="AS3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU3" t="n">
         <v>28</v>
@@ -993,10 +1060,10 @@
         <v>22</v>
       </c>
       <c r="BB3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -1103,19 +1170,19 @@
         <v>-4.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE4" t="n">
         <v>24</v>
       </c>
       <c r="AF4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI4" t="n">
         <v>22</v>
@@ -1127,16 +1194,16 @@
         <v>21</v>
       </c>
       <c r="AL4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM4" t="n">
         <v>25</v>
       </c>
       <c r="AN4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP4" t="n">
         <v>5</v>
@@ -1172,7 +1239,7 @@
         <v>30</v>
       </c>
       <c r="BA4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB4" t="n">
         <v>19</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-4.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE5" t="n">
         <v>12</v>
@@ -1297,7 +1364,7 @@
         <v>14</v>
       </c>
       <c r="AH5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI5" t="n">
         <v>30</v>
@@ -1327,13 +1394,13 @@
         <v>24</v>
       </c>
       <c r="AR5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU5" t="n">
         <v>26</v>
@@ -1360,7 +1427,7 @@
         <v>29</v>
       </c>
       <c r="BC5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>5</v>
       </c>
       <c r="AD6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE6" t="n">
         <v>12</v>
@@ -1479,13 +1546,13 @@
         <v>10</v>
       </c>
       <c r="AH6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI6" t="n">
         <v>24</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK6" t="n">
         <v>18</v>
@@ -1497,7 +1564,7 @@
         <v>28</v>
       </c>
       <c r="AN6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO6" t="n">
         <v>9</v>
@@ -1518,7 +1585,7 @@
         <v>8</v>
       </c>
       <c r="AU6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV6" t="n">
         <v>22</v>
@@ -1533,7 +1600,7 @@
         <v>30</v>
       </c>
       <c r="AZ6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA6" t="n">
         <v>14</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -1649,16 +1716,16 @@
         <v>-7</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH7" t="n">
         <v>2</v>
@@ -1667,13 +1734,13 @@
         <v>26</v>
       </c>
       <c r="AJ7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK7" t="n">
         <v>29</v>
       </c>
       <c r="AL7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM7" t="n">
         <v>20</v>
@@ -1685,7 +1752,7 @@
         <v>19</v>
       </c>
       <c r="AP7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ7" t="n">
         <v>10</v>
@@ -1694,7 +1761,7 @@
         <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT7" t="n">
         <v>16</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1843,7 +1910,7 @@
         <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI8" t="n">
         <v>4</v>
@@ -1855,7 +1922,7 @@
         <v>6</v>
       </c>
       <c r="AL8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM8" t="n">
         <v>7</v>
@@ -1864,7 +1931,7 @@
         <v>7</v>
       </c>
       <c r="AO8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP8" t="n">
         <v>17</v>
@@ -1876,19 +1943,19 @@
         <v>21</v>
       </c>
       <c r="AS8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV8" t="n">
         <v>20</v>
       </c>
       <c r="AW8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX8" t="n">
         <v>27</v>
@@ -1897,7 +1964,7 @@
         <v>6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA8" t="n">
         <v>25</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -2013,22 +2080,22 @@
         <v>-1.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF9" t="n">
         <v>14</v>
       </c>
       <c r="AG9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ9" t="n">
         <v>2</v>
@@ -2040,13 +2107,13 @@
         <v>14</v>
       </c>
       <c r="AM9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN9" t="n">
         <v>9</v>
       </c>
       <c r="AO9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP9" t="n">
         <v>12</v>
@@ -2079,13 +2146,13 @@
         <v>26</v>
       </c>
       <c r="AZ9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA9" t="n">
         <v>3</v>
       </c>
       <c r="BB9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC9" t="n">
         <v>17</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -2117,124 +2184,124 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
         <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.333</v>
+        <v>0.375</v>
       </c>
       <c r="H10" t="n">
         <v>48.6</v>
       </c>
       <c r="I10" t="n">
-        <v>38.4</v>
+        <v>38</v>
       </c>
       <c r="J10" t="n">
-        <v>85.7</v>
+        <v>85.5</v>
       </c>
       <c r="K10" t="n">
-        <v>0.449</v>
+        <v>0.444</v>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="M10" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0.281</v>
+        <v>0.272</v>
       </c>
       <c r="O10" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="P10" t="n">
-        <v>25.2</v>
+        <v>26.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.714</v>
       </c>
       <c r="R10" t="n">
-        <v>14.4</v>
+        <v>14.8</v>
       </c>
       <c r="S10" t="n">
         <v>27.1</v>
       </c>
       <c r="T10" t="n">
-        <v>41.6</v>
+        <v>41.9</v>
       </c>
       <c r="U10" t="n">
-        <v>20.2</v>
+        <v>19.8</v>
       </c>
       <c r="V10" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W10" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="X10" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="Y10" t="n">
         <v>4.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.8</v>
+        <v>22.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="AB10" t="n">
-        <v>100.3</v>
+        <v>100.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.4</v>
+        <v>-2</v>
       </c>
       <c r="AD10" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
       </c>
       <c r="AF10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AG10" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AH10" t="n">
         <v>7</v>
       </c>
       <c r="AI10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL10" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AM10" t="n">
         <v>14</v>
       </c>
       <c r="AN10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AP10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AR10" t="n">
         <v>1</v>
@@ -2243,25 +2310,25 @@
         <v>30</v>
       </c>
       <c r="AT10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU10" t="n">
         <v>21</v>
       </c>
-      <c r="AU10" t="n">
-        <v>19</v>
-      </c>
       <c r="AV10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX10" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AY10" t="n">
         <v>15</v>
       </c>
       <c r="AZ10" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="BA10" t="n">
         <v>12</v>
@@ -2270,7 +2337,7 @@
         <v>13</v>
       </c>
       <c r="BC10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -2377,10 +2444,10 @@
         <v>7.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF11" t="n">
         <v>4</v>
@@ -2389,7 +2456,7 @@
         <v>4</v>
       </c>
       <c r="AH11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI11" t="n">
         <v>3</v>
@@ -2443,10 +2510,10 @@
         <v>4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB11" t="n">
         <v>6</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -2559,10 +2626,10 @@
         <v>2.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF12" t="n">
         <v>9</v>
@@ -2574,7 +2641,7 @@
         <v>2</v>
       </c>
       <c r="AI12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ12" t="n">
         <v>28</v>
@@ -2589,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
@@ -2610,7 +2677,7 @@
         <v>1</v>
       </c>
       <c r="AU12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV12" t="n">
         <v>30</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>9.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2753,7 +2820,7 @@
         <v>1</v>
       </c>
       <c r="AH13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI13" t="n">
         <v>23</v>
@@ -2774,13 +2841,13 @@
         <v>12</v>
       </c>
       <c r="AO13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP13" t="n">
         <v>15</v>
       </c>
       <c r="AQ13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR13" t="n">
         <v>25</v>
@@ -2807,13 +2874,13 @@
         <v>17</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA13" t="n">
         <v>4</v>
       </c>
       <c r="BB13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC13" t="n">
         <v>1</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -2923,10 +2990,10 @@
         <v>4.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="n">
         <v>4</v>
@@ -2935,13 +3002,13 @@
         <v>4</v>
       </c>
       <c r="AH14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI14" t="n">
         <v>1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK14" t="n">
         <v>3</v>
@@ -2962,13 +3029,13 @@
         <v>3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR14" t="n">
         <v>9</v>
       </c>
       <c r="AS14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT14" t="n">
         <v>11</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -3027,28 +3094,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
         <v>7</v>
       </c>
       <c r="G15" t="n">
-        <v>0.417</v>
+        <v>0.364</v>
       </c>
       <c r="H15" t="n">
         <v>48</v>
       </c>
       <c r="I15" t="n">
-        <v>37.4</v>
+        <v>36.5</v>
       </c>
       <c r="J15" t="n">
-        <v>87.3</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.428</v>
+        <v>0.42</v>
       </c>
       <c r="L15" t="n">
         <v>10.2</v>
@@ -3060,73 +3127,73 @@
         <v>0.407</v>
       </c>
       <c r="O15" t="n">
-        <v>14.4</v>
+        <v>14.8</v>
       </c>
       <c r="P15" t="n">
-        <v>20.3</v>
+        <v>21.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.709</v>
+        <v>0.697</v>
       </c>
       <c r="R15" t="n">
-        <v>10.9</v>
+        <v>11.2</v>
       </c>
       <c r="S15" t="n">
-        <v>34.8</v>
+        <v>35.2</v>
       </c>
       <c r="T15" t="n">
-        <v>45.7</v>
+        <v>46.4</v>
       </c>
       <c r="U15" t="n">
-        <v>24.3</v>
+        <v>23.5</v>
       </c>
       <c r="V15" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="W15" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="X15" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Z15" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>17.8</v>
+        <v>18.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.40000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>-4.4</v>
+        <v>-6.2</v>
       </c>
       <c r="AD15" t="n">
         <v>1</v>
       </c>
       <c r="AE15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AF15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG15" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AH15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AJ15" t="n">
         <v>5</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AL15" t="n">
         <v>2</v>
@@ -3141,22 +3208,22 @@
         <v>27</v>
       </c>
       <c r="AP15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AQ15" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AR15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT15" t="n">
         <v>3</v>
       </c>
-      <c r="AT15" t="n">
-        <v>4</v>
-      </c>
       <c r="AU15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AV15" t="n">
         <v>14</v>
@@ -3174,13 +3241,13 @@
         <v>19</v>
       </c>
       <c r="BA15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BC15" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -3209,106 +3276,106 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
         <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5</v>
+        <v>0.444</v>
       </c>
       <c r="H16" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I16" t="n">
-        <v>37.1</v>
+        <v>36.8</v>
       </c>
       <c r="J16" t="n">
-        <v>79.5</v>
+        <v>80.3</v>
       </c>
       <c r="K16" t="n">
-        <v>0.467</v>
+        <v>0.458</v>
       </c>
       <c r="L16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="M16" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="N16" t="n">
         <v>0.313</v>
       </c>
       <c r="O16" t="n">
-        <v>15.5</v>
+        <v>15.8</v>
       </c>
       <c r="P16" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.775</v>
+        <v>0.78</v>
       </c>
       <c r="R16" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="S16" t="n">
-        <v>32.1</v>
+        <v>31</v>
       </c>
       <c r="T16" t="n">
-        <v>41.4</v>
+        <v>40.6</v>
       </c>
       <c r="U16" t="n">
-        <v>23.4</v>
+        <v>22.7</v>
       </c>
       <c r="V16" t="n">
         <v>16.1</v>
       </c>
       <c r="W16" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="X16" t="n">
         <v>3.9</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>94.3</v>
+        <v>94</v>
       </c>
       <c r="AC16" t="n">
-        <v>-2.4</v>
+        <v>-3.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AE16" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AF16" t="n">
         <v>14</v>
       </c>
       <c r="AG16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ16" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AK16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3320,28 +3387,28 @@
         <v>26</v>
       </c>
       <c r="AO16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP16" t="n">
         <v>26</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR16" t="n">
         <v>26</v>
       </c>
       <c r="AS16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV16" t="n">
         <v>16</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>15</v>
       </c>
       <c r="AW16" t="n">
         <v>25</v>
@@ -3350,19 +3417,19 @@
         <v>28</v>
       </c>
       <c r="AY16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA16" t="n">
         <v>17</v>
       </c>
       <c r="BB16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -3469,10 +3536,10 @@
         <v>7.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF17" t="n">
         <v>4</v>
@@ -3481,10 +3548,10 @@
         <v>4</v>
       </c>
       <c r="AH17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3496,7 +3563,7 @@
         <v>6</v>
       </c>
       <c r="AM17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN17" t="n">
         <v>2</v>
@@ -3514,7 +3581,7 @@
         <v>30</v>
       </c>
       <c r="AS17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
@@ -3529,13 +3596,13 @@
         <v>10</v>
       </c>
       <c r="AX17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY17" t="n">
         <v>2</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
         <v>5</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -3651,25 +3718,25 @@
         <v>-8.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE18" t="n">
         <v>27</v>
       </c>
       <c r="AF18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI18" t="n">
         <v>29</v>
       </c>
       <c r="AJ18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK18" t="n">
         <v>27</v>
@@ -3681,10 +3748,10 @@
         <v>21</v>
       </c>
       <c r="AN18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP18" t="n">
         <v>28</v>
@@ -3699,7 +3766,7 @@
         <v>25</v>
       </c>
       <c r="AT18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU18" t="n">
         <v>24</v>
@@ -3711,13 +3778,13 @@
         <v>20</v>
       </c>
       <c r="AX18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA18" t="n">
         <v>21</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -3833,10 +3900,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF19" t="n">
         <v>9</v>
@@ -3845,7 +3912,7 @@
         <v>8</v>
       </c>
       <c r="AH19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI19" t="n">
         <v>6</v>
@@ -3860,7 +3927,7 @@
         <v>13</v>
       </c>
       <c r="AM19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AN19" t="n">
         <v>15</v>
@@ -3893,13 +3960,13 @@
         <v>3</v>
       </c>
       <c r="AX19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY19" t="n">
         <v>27</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA19" t="n">
         <v>9</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -4015,22 +4082,22 @@
         <v>1.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF20" t="n">
         <v>18</v>
       </c>
-      <c r="AF20" t="n">
-        <v>17</v>
-      </c>
       <c r="AG20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ20" t="n">
         <v>11</v>
@@ -4048,7 +4115,7 @@
         <v>3</v>
       </c>
       <c r="AO20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP20" t="n">
         <v>14</v>
@@ -4063,7 +4130,7 @@
         <v>24</v>
       </c>
       <c r="AT20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU20" t="n">
         <v>14</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -4197,28 +4264,28 @@
         <v>-5.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE21" t="n">
         <v>24</v>
       </c>
       <c r="AF21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI21" t="n">
         <v>21</v>
       </c>
       <c r="AJ21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL21" t="n">
         <v>8</v>
@@ -4227,7 +4294,7 @@
         <v>3</v>
       </c>
       <c r="AN21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4263,16 +4330,16 @@
         <v>10</v>
       </c>
       <c r="AZ21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB21" t="n">
         <v>23</v>
       </c>
       <c r="BC21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>2.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE22" t="n">
         <v>9</v>
@@ -4391,7 +4458,7 @@
         <v>7</v>
       </c>
       <c r="AH22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI22" t="n">
         <v>20</v>
@@ -4400,10 +4467,10 @@
         <v>18</v>
       </c>
       <c r="AK22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM22" t="n">
         <v>23</v>
@@ -4421,16 +4488,16 @@
         <v>2</v>
       </c>
       <c r="AR22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS22" t="n">
         <v>5</v>
       </c>
       <c r="AT22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV22" t="n">
         <v>23</v>
@@ -4445,7 +4512,7 @@
         <v>8</v>
       </c>
       <c r="AZ22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -4561,28 +4628,28 @@
         <v>0.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF23" t="n">
         <v>18</v>
       </c>
-      <c r="AF23" t="n">
-        <v>17</v>
-      </c>
       <c r="AG23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI23" t="n">
         <v>11</v>
       </c>
       <c r="AJ23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL23" t="n">
         <v>15</v>
@@ -4627,7 +4694,7 @@
         <v>28</v>
       </c>
       <c r="AZ23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA23" t="n">
         <v>26</v>
@@ -4636,7 +4703,7 @@
         <v>15</v>
       </c>
       <c r="BC23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -4743,16 +4810,16 @@
         <v>-6.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE24" t="n">
         <v>12</v>
       </c>
       <c r="AF24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH24" t="n">
         <v>2</v>
@@ -4794,7 +4861,7 @@
         <v>10</v>
       </c>
       <c r="AU24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AV24" t="n">
         <v>26</v>
@@ -4809,13 +4876,13 @@
         <v>29</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA24" t="n">
         <v>20</v>
       </c>
       <c r="BB24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC24" t="n">
         <v>27</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>3</v>
       </c>
       <c r="AD25" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE25" t="n">
         <v>12</v>
@@ -4937,10 +5004,10 @@
         <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ25" t="n">
         <v>19</v>
@@ -4952,7 +5019,7 @@
         <v>11</v>
       </c>
       <c r="AM25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN25" t="n">
         <v>14</v>
@@ -4961,7 +5028,7 @@
         <v>20</v>
       </c>
       <c r="AP25" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ25" t="n">
         <v>15</v>
@@ -4985,7 +5052,7 @@
         <v>5</v>
       </c>
       <c r="AX25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY25" t="n">
         <v>8</v>
@@ -4997,7 +5064,7 @@
         <v>23</v>
       </c>
       <c r="BB25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -5029,85 +5096,85 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F26" t="n">
         <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8</v>
+        <v>0.778</v>
       </c>
       <c r="H26" t="n">
-        <v>48.5</v>
+        <v>48</v>
       </c>
       <c r="I26" t="n">
-        <v>39.4</v>
+        <v>38.9</v>
       </c>
       <c r="J26" t="n">
-        <v>86.09999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="K26" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L26" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="M26" t="n">
-        <v>23.8</v>
+        <v>22.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0.42</v>
+        <v>0.413</v>
       </c>
       <c r="O26" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="P26" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.763</v>
+        <v>0.765</v>
       </c>
       <c r="R26" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="S26" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="T26" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
       <c r="U26" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="V26" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W26" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="X26" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="Y26" t="n">
         <v>2.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.1</v>
+        <v>18.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>104.6</v>
+        <v>103.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
@@ -5119,31 +5186,31 @@
         <v>3</v>
       </c>
       <c r="AH26" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AI26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AJ26" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AK26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM26" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AN26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ26" t="n">
         <v>14</v>
@@ -5167,19 +5234,19 @@
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AY26" t="n">
         <v>1</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BA26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BC26" t="n">
         <v>7</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -5211,28 +5278,28 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
         <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G27" t="n">
-        <v>0.222</v>
+        <v>0.25</v>
       </c>
       <c r="H27" t="n">
         <v>48</v>
       </c>
       <c r="I27" t="n">
-        <v>34.9</v>
+        <v>35.1</v>
       </c>
       <c r="J27" t="n">
-        <v>83.59999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.418</v>
+        <v>0.423</v>
       </c>
       <c r="L27" t="n">
         <v>7.1</v>
@@ -5241,76 +5308,76 @@
         <v>22.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0.318</v>
+        <v>0.32</v>
       </c>
       <c r="O27" t="n">
-        <v>16.1</v>
+        <v>16.5</v>
       </c>
       <c r="P27" t="n">
-        <v>20.7</v>
+        <v>21.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.78</v>
+        <v>0.781</v>
       </c>
       <c r="R27" t="n">
         <v>10.8</v>
       </c>
       <c r="S27" t="n">
-        <v>28.7</v>
+        <v>29.3</v>
       </c>
       <c r="T27" t="n">
-        <v>39.4</v>
+        <v>40</v>
       </c>
       <c r="U27" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="V27" t="n">
-        <v>12.2</v>
+        <v>12.8</v>
       </c>
       <c r="W27" t="n">
         <v>8</v>
       </c>
       <c r="X27" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>22.6</v>
+        <v>22.9</v>
       </c>
       <c r="AA27" t="n">
         <v>20.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>93</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4.9</v>
+        <v>-4.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AE27" t="n">
         <v>27</v>
       </c>
       <c r="AF27" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AG27" t="n">
         <v>27</v>
       </c>
       <c r="AH27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI27" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AJ27" t="n">
         <v>14</v>
       </c>
       <c r="AK27" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL27" t="n">
         <v>18</v>
@@ -5325,7 +5392,7 @@
         <v>18</v>
       </c>
       <c r="AP27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ27" t="n">
         <v>7</v>
@@ -5334,10 +5401,10 @@
         <v>18</v>
       </c>
       <c r="AS27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT27" t="n">
         <v>27</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>28</v>
       </c>
       <c r="AU27" t="n">
         <v>22</v>
@@ -5349,13 +5416,13 @@
         <v>16</v>
       </c>
       <c r="AX27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY27" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AZ27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BA27" t="n">
         <v>18</v>
@@ -5364,7 +5431,7 @@
         <v>26</v>
       </c>
       <c r="BC27" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="AD28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5483,13 +5550,13 @@
         <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI28" t="n">
         <v>5</v>
       </c>
       <c r="AJ28" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AK28" t="n">
         <v>5</v>
@@ -5516,19 +5583,19 @@
         <v>28</v>
       </c>
       <c r="AS28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT28" t="n">
         <v>12</v>
       </c>
       <c r="AU28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV28" t="n">
         <v>6</v>
       </c>
       <c r="AW28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX28" t="n">
         <v>24</v>
@@ -5543,7 +5610,7 @@
         <v>30</v>
       </c>
       <c r="BB28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC28" t="n">
         <v>2</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -5575,121 +5642,121 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E29" t="n">
         <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G29" t="n">
-        <v>0.364</v>
+        <v>0.4</v>
       </c>
       <c r="H29" t="n">
-        <v>49.4</v>
+        <v>49</v>
       </c>
       <c r="I29" t="n">
-        <v>35.2</v>
+        <v>34.5</v>
       </c>
       <c r="J29" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K29" t="n">
-        <v>0.419</v>
+        <v>0.416</v>
       </c>
       <c r="L29" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="M29" t="n">
-        <v>20.1</v>
+        <v>20.4</v>
       </c>
       <c r="N29" t="n">
-        <v>0.326</v>
+        <v>0.338</v>
       </c>
       <c r="O29" t="n">
-        <v>20</v>
+        <v>19.7</v>
       </c>
       <c r="P29" t="n">
-        <v>26.1</v>
+        <v>25.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.767</v>
+        <v>0.77</v>
       </c>
       <c r="R29" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="S29" t="n">
-        <v>30.7</v>
+        <v>30.2</v>
       </c>
       <c r="T29" t="n">
-        <v>44.7</v>
+        <v>44.1</v>
       </c>
       <c r="U29" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="V29" t="n">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="W29" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X29" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y29" t="n">
         <v>6.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>96.90000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>-0.2</v>
+        <v>0.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF29" t="n">
         <v>18</v>
       </c>
-      <c r="AF29" t="n">
-        <v>23</v>
-      </c>
       <c r="AG29" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AH29" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AI29" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AJ29" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AK29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM29" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AN29" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AO29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ29" t="n">
         <v>13</v>
@@ -5698,7 +5765,7 @@
         <v>2</v>
       </c>
       <c r="AS29" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AT29" t="n">
         <v>9</v>
@@ -5710,25 +5777,25 @@
         <v>7</v>
       </c>
       <c r="AW29" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AX29" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AY29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ29" t="n">
         <v>27</v>
       </c>
       <c r="BA29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-11.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE30" t="n">
         <v>30</v>
@@ -5847,7 +5914,7 @@
         <v>30</v>
       </c>
       <c r="AH30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI30" t="n">
         <v>28</v>
@@ -5865,7 +5932,7 @@
         <v>24</v>
       </c>
       <c r="AN30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO30" t="n">
         <v>16</v>
@@ -5904,7 +5971,7 @@
         <v>20</v>
       </c>
       <c r="BA30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB30" t="n">
         <v>30</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
@@ -6017,16 +6084,16 @@
         <v>-4.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE31" t="n">
         <v>27</v>
       </c>
       <c r="AF31" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH31" t="n">
         <v>1</v>
@@ -6038,7 +6105,7 @@
         <v>4</v>
       </c>
       <c r="AK31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL31" t="n">
         <v>3</v>
@@ -6056,19 +6123,19 @@
         <v>18</v>
       </c>
       <c r="AQ31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR31" t="n">
         <v>10</v>
       </c>
       <c r="AS31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT31" t="n">
         <v>19</v>
       </c>
       <c r="AU31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV31" t="n">
         <v>18</v>
@@ -6077,7 +6144,7 @@
         <v>5</v>
       </c>
       <c r="AX31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY31" t="n">
         <v>12</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>11-17-2013-14</t>
+          <t>2013-11-17</t>
         </is>
       </c>
     </row>
